--- a/signup_forms/005_open_science_education_community_registration_form--signup_forms.xlsx
+++ b/signup_forms/005_open_science_education_community_registration_form--signup_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>biology</t>
+          <t>earth_and_planetary_science</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Earth and Planetary Science</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>earth_and_planetary_science</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Earth and Planetary Science</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>mathematics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Mathematics</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mathematics</t>
+          <t>medicine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Medicine</t>
         </is>
       </c>
     </row>
@@ -1072,29 +1072,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>medicine</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>science_focus_area_choices</t>
+          <t>educational_background_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bachelor's</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bachelor's</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -1123,29 +1123,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>master's</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Master's</t>
+          <t>PhD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>educational_background_choices</t>
+          <t>research_interests_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>phd</t>
+          <t>artificial_intelligence</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>artificial_intelligence</t>
+          <t>biomechanics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biomechanics</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>biomechanics</t>
+          <t>computational_biology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Biomechanics</t>
+          <t>Computational Biology</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>computational_biology</t>
+          <t>data_science</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Computational Biology</t>
+          <t>Data Science</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>data_science</t>
+          <t>machine_learning</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Machine Learning</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>machine_learning</t>
+          <t>neuroscience</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Neuroscience</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>neuroscience</t>
+          <t>quantum_mechanics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Neuroscience</t>
+          <t>Quantum Mechanics</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>quantum_mechanics</t>
+          <t>robotics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Quantum Mechanics</t>
+          <t>Robotics</t>
         </is>
       </c>
     </row>
@@ -1276,29 +1276,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>robotics</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Sustainability</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>research_interests_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sustainability</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sustainability</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>leadership</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>project_management</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -1361,29 +1361,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>team_management</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Team Management</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>language_spoken_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>team_management</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Team Management</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mandarin</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>japanese</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>portuguese</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Portuguese</t>
         </is>
       </c>
     </row>
@@ -1497,29 +1497,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>portuguese</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portuguese</t>
+          <t>Italian</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>language_spoken_choices</t>
+          <t>agree_terms_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>italian</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italian</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1531,27 +1531,10 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>agree_terms_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
